--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_maule.xlsx
@@ -66,12 +66,12 @@
     <t xml:space="preserve">Romeral</t>
   </si>
   <si>
+    <t xml:space="preserve">Rauco</t>
+  </si>
+  <si>
     <t xml:space="preserve">Licantén</t>
   </si>
   <si>
-    <t xml:space="preserve">Rauco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Retiro</t>
   </si>
   <si>
@@ -81,12 +81,12 @@
     <t xml:space="preserve">Pelluhue</t>
   </si>
   <si>
+    <t xml:space="preserve">Vichuquén</t>
+  </si>
+  <si>
     <t xml:space="preserve">Empedrado</t>
   </si>
   <si>
-    <t xml:space="preserve">Vichuquén</t>
-  </si>
-  <si>
     <t xml:space="preserve">Molina</t>
   </si>
   <si>
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:40</t>
+    <t xml:space="preserve">2026-09-09 22:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -743,7 +743,7 @@
         <v>16</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>7303</v>
+        <v>7305</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2019</v>
@@ -760,7 +760,7 @@
         <v>17</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>7305</v>
+        <v>7303</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2019</v>
@@ -828,7 +828,7 @@
         <v>21</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>7104</v>
+        <v>7309</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2019</v>
@@ -845,7 +845,7 @@
         <v>22</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>7309</v>
+        <v>7104</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2019</v>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:26</t>
+    <t xml:space="preserve">2026-09-12 19:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_maule.xlsx
@@ -66,12 +66,12 @@
     <t xml:space="preserve">Romeral</t>
   </si>
   <si>
+    <t xml:space="preserve">Licantén</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rauco</t>
   </si>
   <si>
-    <t xml:space="preserve">Licantén</t>
-  </si>
-  <si>
     <t xml:space="preserve">Retiro</t>
   </si>
   <si>
@@ -81,12 +81,12 @@
     <t xml:space="preserve">Pelluhue</t>
   </si>
   <si>
+    <t xml:space="preserve">Empedrado</t>
+  </si>
+  <si>
     <t xml:space="preserve">Vichuquén</t>
   </si>
   <si>
-    <t xml:space="preserve">Empedrado</t>
-  </si>
-  <si>
     <t xml:space="preserve">Molina</t>
   </si>
   <si>
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:43</t>
+    <t xml:space="preserve">2026-09-24 00:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -743,7 +743,7 @@
         <v>16</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>7305</v>
+        <v>7303</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2019</v>
@@ -760,7 +760,7 @@
         <v>17</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>7303</v>
+        <v>7305</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2019</v>
@@ -828,7 +828,7 @@
         <v>21</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>7309</v>
+        <v>7104</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2019</v>
@@ -845,7 +845,7 @@
         <v>22</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>7104</v>
+        <v>7309</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2019</v>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:21</t>
+    <t xml:space="preserve">2026-09-27 22:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:10</t>
+    <t xml:space="preserve">2026-10-01 20:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:50</t>
+    <t xml:space="preserve">2026-10-02 13:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:17</t>
+    <t xml:space="preserve">2026-10-05 07:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
